--- a/Packages/cn.etetet.config/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.config/Luban/Config/Base/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.excel/Luban/Config/Base/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.config/Luban/Config/Base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1141A4-E2E0-7F42-9A47-27770D0B210E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7D0098-DCC5-DE4E-97BB-F56EC2CF9FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34620" yWindow="12760" windowWidth="31280" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>Text</t>
   </si>
   <si>
-    <t>../../../../cn.etetet.quest/Luban/Config/Datas/Text.xlsx,../../../../cn.etetet.statesync/Luban/Config/Datas/Text.xlsx,../../../../cn.etetet.spell/Luban/Config/Datas/Text.xlsx</t>
+    <t>Packages/cn.etetet.quest/Luban/Config/Datas/Text.xlsx,Packages/cn.etetet.statesync/Luban/Config/Datas/Text.xlsx,Packages/cn.etetet.spell/Luban/Config/Datas/Text.xlsx</t>
   </si>
 </sst>
 </file>
